--- a/smartshop/EvidenceBasedAdaptiveUI/reports/02_exploratory_data_analysis/tables/mobile/mobile_category_display.xlsx
+++ b/smartshop/EvidenceBasedAdaptiveUI/reports/02_exploratory_data_analysis/tables/mobile/mobile_category_display.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="C2" t="n">
-        <v>42.5</v>
+        <v>43.75</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="C3" t="n">
-        <v>40</v>
+        <v>38.84</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C4" t="n">
-        <v>17.5</v>
+        <v>17.41</v>
       </c>
     </row>
   </sheetData>
